--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,37 +28,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -451,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -537,27 +525,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t/>
   </si>
   <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -31,22 +31,61 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>20125391</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG AC/SPT780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
   </si>
 </sst>
 </file>
@@ -439,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -522,10 +561,130 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t/>
   </si>
   <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
+    <t>20130077</t>
+  </si>
+  <si>
+    <t>BABY HP PNKFONG M-32</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -31,61 +31,19 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
+    <t>20130078</t>
+  </si>
+  <si>
+    <t>BABY HP PNKFONG L-28</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>20125391</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG AC/SPT780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
   </si>
 </sst>
 </file>
@@ -478,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -541,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -549,10 +507,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -561,130 +519,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20130077</t>
-  </si>
-  <si>
-    <t>BABY HP PNKFONG M-32</t>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,22 +28,49 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20130078</t>
-  </si>
-  <si>
-    <t>BABY HP PNKFONG L-28</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
+  </si>
+  <si>
+    <t>20140872</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT XL-32S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ1 P/SGR1.5</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK DET+SF RB 1.4</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
   </si>
 </sst>
 </file>
@@ -436,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -519,10 +546,90 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
+    <t>20098000</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 28+2S L</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -31,46 +31,70 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20137024</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT M-44</t>
-  </si>
-  <si>
-    <t>20140872</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT XL-32S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
+    <t>20098001</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 26+2S XL</t>
+  </si>
+  <si>
+    <t>20108881</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 32+2S M</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK DET+SF RB 1.4</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 690</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -463,13 +487,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -549,27 +573,27 @@
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -586,10 +610,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -606,10 +630,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -626,10 +650,70 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>20098000</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 28+2S L</t>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,73 +28,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20098001</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 26+2S XL</t>
-  </si>
-  <si>
-    <t>20108881</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 32+2S M</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -487,13 +430,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,170 +493,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
+    <t>20072919</t>
+  </si>
+  <si>
+    <t>BABY HAPY PANTS L 20</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -31,13 +31,16 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -496,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20072919</t>
-  </si>
-  <si>
-    <t>BABY HAPY PANTS L 20</t>
+    <t>20077483</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS26 XL</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20041257</t>
+  </si>
+  <si>
+    <t>MAMY/P DIAPERS S-24S</t>
   </si>
   <si>
     <t>2</t>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -31,16 +31,16 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20041257</t>
-  </si>
-  <si>
-    <t>MAMY/P DIAPERS S-24S</t>
+    <t>10038967</t>
+  </si>
+  <si>
+    <t>NICE FC TISU LVG1000</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT</t>
+    <t>RT</t>
   </si>
 </sst>
 </file>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t/>
   </si>
   <si>
-    <t>20077483</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS26 XL</t>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,19 +28,40 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10038967</t>
-  </si>
-  <si>
-    <t>NICE FC TISU LVG1000</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 720</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTG PRPL 720</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 720G</t>
   </si>
 </sst>
 </file>
@@ -433,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -499,7 +520,67 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,40 +28,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>20021393</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL20</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 720</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTG PRPL 720</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -454,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -517,7 +502,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -525,10 +510,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -537,50 +522,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO/KLN SOFT P/RS1.44</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,25 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>20021393</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL20</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SOKLN RED/MG&amp;B1.44KG</t>
+  </si>
+  <si>
+    <t>20099414</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT PRPL1.44</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN EDP BLNC 1.44</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN EDP D.LS 144</t>
   </si>
 </sst>
 </file>
@@ -439,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -522,10 +534,50 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO/KLN SOFT P/RS1.44</t>
+    <t>20054750</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ PRFM 510</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,37 +28,73 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20093188</t>
+  </si>
+  <si>
+    <t>RINSO MLTO GLD LQ510</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>20122879</t>
+  </si>
+  <si>
+    <t>RNSO MLTO KRN STR510</t>
+  </si>
+  <si>
+    <t>20137793</t>
+  </si>
+  <si>
+    <t>RINSO ROSE FRESH 510</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140001</t>
+  </si>
+  <si>
+    <t>RINSO PURE LIQ 510G</t>
+  </si>
+  <si>
+    <t>20098000</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 28+2S L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20098001</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 26+2S XL</t>
+  </si>
+  <si>
+    <t>20108881</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 32+2S M</t>
+  </si>
+  <si>
+    <t>20139956</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 38S NB-S</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SOKLN RED/MG&amp;B1.44KG</t>
-  </si>
-  <si>
-    <t>20099414</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT PRPL1.44</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SO KLN EDP BLNC 1.44</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SO KLN EDP D.LS 144</t>
   </si>
 </sst>
 </file>
@@ -451,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -554,30 +590,130 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20054750</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ PRFM 510</t>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>KAOATT DP SC 1.5 KG</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,73 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20093188</t>
-  </si>
-  <si>
-    <t>RINSO MLTO GLD LQ510</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
-    <t>20122879</t>
-  </si>
-  <si>
-    <t>RNSO MLTO KRN STR510</t>
-  </si>
-  <si>
-    <t>20137793</t>
-  </si>
-  <si>
-    <t>RINSO ROSE FRESH 510</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140001</t>
-  </si>
-  <si>
-    <t>RINSO PURE LIQ 510G</t>
-  </si>
-  <si>
-    <t>20098000</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 28+2S L</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>KAOATT DP PS 1.5 KG</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>KAOATT DP RB 1.4 KG</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>KAOATT DP PB 1.4 KG</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JNP 950 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20098001</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 26+2S XL</t>
-  </si>
-  <si>
-    <t>20108881</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 32+2S M</t>
-  </si>
-  <si>
-    <t>20139956</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 38S NB-S</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>PT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -487,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -610,110 +574,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>KAOATT DP SC 1.5 KG</t>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,37 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>KAOATT DP PS 1.5 KG</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>KAOATT DP RB 1.4 KG</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>KAOATT DP PB 1.4 KG</t>
-  </si>
-  <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JNP 950 ML</t>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20120921</t>
+  </si>
+  <si>
+    <t>GIV BW GLOW.WH 800ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -514,70 +496,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,19 +28,85 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20120921</t>
-  </si>
-  <si>
-    <t>GIV BW GLOW.WH 800ML</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 600</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 600</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V600</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
+  </si>
+  <si>
+    <t>20142010</t>
+  </si>
+  <si>
+    <t>ROYALE MTCHA BLS 600</t>
   </si>
 </sst>
 </file>
@@ -433,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -496,10 +562,210 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
   <si>
     <t/>
   </si>
@@ -37,76 +37,34 @@
     <t>SNLGHT BIO BLBR 870G</t>
   </si>
   <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 600</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 600</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V600</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>20142010</t>
-  </si>
-  <si>
-    <t>ROYALE MTCHA BLS 600</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
+  </si>
+  <si>
+    <t>20140872</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT XL-32S</t>
+  </si>
+  <si>
+    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -499,16 +457,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,8 +486,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -544,11 +509,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -562,18 +527,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -582,18 +547,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -602,13 +567,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -622,150 +587,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,57 +11,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
+  </si>
+  <si>
+    <t>DU3BMKT</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20001546</t>
+  </si>
+  <si>
+    <t>MITU TIS.G/P BLU2X50</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20035113</t>
+  </si>
+  <si>
+    <t>MITU WIPE BLUE BB 40</t>
+  </si>
+  <si>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20112491</t>
   </si>
   <si>
     <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
-    <t>DU3BMKT</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
+    <t>10038967</t>
+  </si>
+  <si>
+    <t>NICE FC TISU LVG1000</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137024</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT M-44</t>
-  </si>
-  <si>
-    <t>20140872</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT XL-32S</t>
   </si>
   <si>
     <t>RT</t>
@@ -457,17 +472,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,14 +500,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -509,11 +517,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -527,13 +535,13 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -547,18 +555,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -567,18 +575,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -587,10 +595,50 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2X50'S</t>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -31,55 +31,34 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20001546</t>
-  </si>
-  <si>
-    <t>MITU TIS.G/P BLU2X50</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20035113</t>
-  </si>
-  <si>
-    <t>MITU WIPE BLUE BB 40</t>
-  </si>
-  <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10038967</t>
-  </si>
-  <si>
-    <t>NICE FC TISU LVG1000</t>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20101378</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE PNK 50</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20121413</t>
+  </si>
+  <si>
+    <t>KDMO B.WP ALOE 2X50S</t>
   </si>
 </sst>
 </file>
@@ -472,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -535,18 +514,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -555,18 +534,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -575,70 +554,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,25 +28,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20101378</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE PNK 50</t>
+    <t>20060393</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CLSC 400</t>
   </si>
   <si>
     <t>3</t>
@@ -55,10 +52,31 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
+    <t>20060392</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CARING 400</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20063269</t>
+  </si>
+  <si>
+    <t>NUVO CAIR NATURE 400</t>
+  </si>
+  <si>
+    <t>20114112</t>
+  </si>
+  <si>
+    <t>NUVO FRS.PRO LMN 400</t>
+  </si>
+  <si>
+    <t>20138658</t>
+  </si>
+  <si>
+    <t>NUVO BW HYGIENIC 400</t>
   </si>
 </sst>
 </file>
@@ -451,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -517,15 +535,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -534,18 +552,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -554,10 +572,70 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20098000</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 28+2S L</t>
+    <t>10008989</t>
+  </si>
+  <si>
+    <t>BIMOLI MYK.GRG REF2L</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,37 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20098001</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 26+2S XL</t>
-  </si>
-  <si>
-    <t>20108881</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 32+2S M</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10010805</t>
+  </si>
+  <si>
+    <t>SANIA MNYK GR PCH 2L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
+    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -514,70 +496,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
